--- a/stock.xlsx
+++ b/stock.xlsx
@@ -7361,7 +7361,7 @@
     <t xml:space="preserve">:</t>
   </si>
   <si>
-    <t xml:space="preserve">03-10-2026 16:32:21</t>
+    <t xml:space="preserve">03-10-2026 17:01:17</t>
   </si>
   <si>
     <t xml:space="preserve">03-10-2026</t>
@@ -8096,7 +8096,7 @@
     <t xml:space="preserve">GLZ 8353-19 3740205</t>
   </si>
   <si>
-    <t xml:space="preserve">FD D105 2429185</t>
+    <t xml:space="preserve">FEDOR D105 2429185</t>
   </si>
   <si>
     <t xml:space="preserve">GLZ L1381-98 374120</t>
@@ -8186,7 +8186,7 @@
     <t xml:space="preserve">NE 789 364021</t>
   </si>
   <si>
-    <t xml:space="preserve">FD E105 1823165</t>
+    <t xml:space="preserve">FEDOR E105 1823165</t>
   </si>
   <si>
     <t xml:space="preserve">BALANCE 1126 364025</t>
@@ -10145,7 +10145,7 @@
     <t xml:space="preserve">ALI 1715-A1 303521</t>
   </si>
   <si>
-    <t xml:space="preserve">FD D160-1 2530185</t>
+    <t xml:space="preserve">FEDOR D160-1 2530185</t>
   </si>
   <si>
     <t xml:space="preserve">NE 38073 333824</t>
@@ -12938,7 +12938,7 @@
     <t xml:space="preserve">DLX 565B-5 3640215</t>
   </si>
   <si>
-    <t xml:space="preserve">FD B077-7H 3540205</t>
+    <t xml:space="preserve">FEDOR B077-7H 3540205</t>
   </si>
   <si>
     <t xml:space="preserve">NE 9175 3641265</t>
@@ -14501,7 +14501,7 @@
     <t xml:space="preserve">BOL 2026 293425</t>
   </si>
   <si>
-    <t xml:space="preserve">FD E106-1 1823185</t>
+    <t xml:space="preserve">FEDOR E106-1 1823185</t>
   </si>
   <si>
     <t xml:space="preserve">BALANCE 889-V1 374030</t>
@@ -20196,7 +20196,7 @@
       <c r="D277" s="4"/>
       <c r="E277" s="4"/>
       <c r="F277" s="7" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G277" s="4" t="s">
         <v>4898</v>
@@ -23730,7 +23730,7 @@
       <c r="D463" s="4"/>
       <c r="E463" s="4"/>
       <c r="F463" s="7" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G463" s="4" t="s">
         <v>4898</v>
@@ -25820,7 +25820,7 @@
       <c r="D573" s="4"/>
       <c r="E573" s="4"/>
       <c r="F573" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G573" s="4" t="s">
         <v>4898</v>
@@ -30095,7 +30095,7 @@
       <c r="D798" s="4"/>
       <c r="E798" s="4"/>
       <c r="F798" s="7" t="n">
-        <v>-78</v>
+        <v>0</v>
       </c>
       <c r="G798" s="4" t="s">
         <v>4898</v>
@@ -30893,7 +30893,7 @@
       <c r="D840" s="4"/>
       <c r="E840" s="4"/>
       <c r="F840" s="7" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="G840" s="4" t="s">
         <v>4898</v>
@@ -34313,7 +34313,7 @@
       <c r="D1020" s="4"/>
       <c r="E1020" s="4"/>
       <c r="F1020" s="7" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G1020" s="4" t="s">
         <v>4898</v>
@@ -36061,7 +36061,7 @@
       <c r="D1112" s="4"/>
       <c r="E1112" s="4"/>
       <c r="F1112" s="7" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G1112" s="4" t="s">
         <v>4898</v>
@@ -36365,7 +36365,7 @@
       <c r="D1128" s="4"/>
       <c r="E1128" s="4"/>
       <c r="F1128" s="7" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G1128" s="4" t="s">
         <v>4898</v>
@@ -39880,7 +39880,7 @@
       <c r="D1313" s="4"/>
       <c r="E1313" s="4"/>
       <c r="F1313" s="7" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G1313" s="4" t="s">
         <v>4898</v>
@@ -41818,7 +41818,7 @@
       <c r="D1415" s="4"/>
       <c r="E1415" s="4"/>
       <c r="F1415" s="7" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="G1415" s="4" t="s">
         <v>4898</v>
@@ -52116,7 +52116,7 @@
       <c r="D1957" s="4"/>
       <c r="E1957" s="4"/>
       <c r="F1957" s="7" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G1957" s="4" t="s">
         <v>4898</v>
@@ -57873,7 +57873,7 @@
       <c r="D2260" s="4"/>
       <c r="E2260" s="4"/>
       <c r="F2260" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2260" s="4" t="s">
         <v>4898</v>
@@ -58937,7 +58937,7 @@
       <c r="D2316" s="4"/>
       <c r="E2316" s="4"/>
       <c r="F2316" s="7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G2316" s="4" t="s">
         <v>4898</v>
